--- a/data/availability/projects/mountain-view/mountain-view-jirian.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-jirian.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1309,7 +1309,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1366,7 +1365,6 @@
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1399,7 +1397,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1423,7 +1421,6 @@
       <c r="G4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1456,7 +1453,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1480,7 +1477,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1513,7 +1509,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1537,7 +1533,6 @@
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1570,7 +1565,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1594,7 +1589,6 @@
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1627,7 +1621,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1651,7 +1645,6 @@
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1684,7 +1677,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1708,7 +1701,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1741,7 +1733,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1765,7 +1757,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1798,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1822,7 +1813,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1855,7 +1845,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1879,7 +1869,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1912,7 +1901,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1936,7 +1925,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1969,7 +1957,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1993,7 +1981,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2026,7 +2013,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2050,7 +2037,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2107,7 +2093,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2140,7 +2125,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2164,7 +2149,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2197,7 +2181,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2221,7 +2205,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2254,7 +2237,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2278,7 +2261,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2311,7 +2293,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2335,7 +2317,6 @@
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2368,7 +2349,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2392,7 +2373,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2425,7 +2405,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2449,7 +2429,6 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2482,7 +2461,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2506,7 +2485,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2539,7 +2517,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2563,7 +2541,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2596,7 +2573,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2620,7 +2597,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2653,7 +2629,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2677,7 +2653,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2710,7 +2685,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2734,7 +2709,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2767,7 +2741,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2791,7 +2765,6 @@
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2824,7 +2797,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2848,7 +2821,6 @@
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2881,7 +2853,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2905,7 +2877,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2938,7 +2909,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2962,7 +2933,6 @@
       <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2995,7 +2965,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3019,7 +2989,6 @@
       <c r="G32" t="n">
         <v>0</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3052,7 +3021,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3076,7 +3045,6 @@
       <c r="G33" t="n">
         <v>0</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3109,7 +3077,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3133,7 +3101,6 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3166,7 +3133,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3190,7 +3157,6 @@
       <c r="G35" t="n">
         <v>0</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3223,7 +3189,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3247,7 +3213,6 @@
       <c r="G36" t="n">
         <v>0</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3280,7 +3245,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3304,7 +3269,6 @@
       <c r="G37" t="n">
         <v>0</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3337,7 +3301,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3361,7 +3325,6 @@
       <c r="G38" t="n">
         <v>0</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3394,7 +3357,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3418,7 +3381,6 @@
       <c r="G39" t="n">
         <v>0</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3451,7 +3413,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3475,7 +3437,6 @@
       <c r="G40" t="n">
         <v>0</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3508,7 +3469,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3532,7 +3493,6 @@
       <c r="G41" t="n">
         <v>0</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3565,7 +3525,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3589,7 +3549,6 @@
       <c r="G42" t="n">
         <v>0</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3622,7 +3581,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3646,7 +3605,6 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3679,7 +3637,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3703,7 +3661,6 @@
       <c r="G44" t="n">
         <v>0</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3736,7 +3693,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3760,7 +3717,6 @@
       <c r="G45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3793,7 +3749,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3817,7 +3773,6 @@
       <c r="G46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3850,7 +3805,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3874,7 +3829,6 @@
       <c r="G47" t="n">
         <v>0</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3907,7 +3861,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3931,7 +3885,6 @@
       <c r="G48" t="n">
         <v>40</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3964,7 +3917,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3988,7 +3941,6 @@
       <c r="G49" t="n">
         <v>40</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4021,7 +3973,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4045,7 +3997,6 @@
       <c r="G50" t="n">
         <v>85</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4078,7 +4029,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I-Villa Garden</t>
+          <t>Duplex</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4102,7 +4053,6 @@
       <c r="G51" t="n">
         <v>40</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4159,7 +4109,6 @@
       <c r="G52" t="n">
         <v>0</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4216,7 +4165,6 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4273,7 +4221,6 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4306,7 +4253,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4330,7 +4277,6 @@
       <c r="G55" t="n">
         <v>70</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4387,7 +4333,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4420,7 +4365,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4444,7 +4389,6 @@
       <c r="G57" t="n">
         <v>70</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4477,7 +4421,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4501,7 +4445,6 @@
       <c r="G58" t="n">
         <v>70</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4558,7 +4501,6 @@
       <c r="G59" t="n">
         <v>0</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4615,7 +4557,6 @@
       <c r="G60" t="n">
         <v>0</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4672,7 +4613,6 @@
       <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4729,7 +4669,6 @@
       <c r="G62" t="n">
         <v>0</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4762,7 +4701,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4786,7 +4725,6 @@
       <c r="G63" t="n">
         <v>70</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4843,7 +4781,6 @@
       <c r="G64" t="n">
         <v>0</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4900,7 +4837,6 @@
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4957,7 +4893,6 @@
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5014,7 +4949,6 @@
       <c r="G67" t="n">
         <v>0</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5071,7 +5005,6 @@
       <c r="G68" t="n">
         <v>0</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5128,7 +5061,6 @@
       <c r="G69" t="n">
         <v>0</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5185,7 +5117,6 @@
       <c r="G70" t="n">
         <v>0</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5242,7 +5173,6 @@
       <c r="G71" t="n">
         <v>0</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5275,7 +5205,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5299,7 +5229,6 @@
       <c r="G72" t="n">
         <v>70</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5332,7 +5261,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5356,7 +5285,6 @@
       <c r="G73" t="n">
         <v>70</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5413,7 +5341,6 @@
       <c r="G74" t="n">
         <v>0</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5470,7 +5397,6 @@
       <c r="G75" t="n">
         <v>0</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5527,7 +5453,6 @@
       <c r="G76" t="n">
         <v>0</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5584,7 +5509,6 @@
       <c r="G77" t="n">
         <v>0</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5641,7 +5565,6 @@
       <c r="G78" t="n">
         <v>0</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5698,7 +5621,6 @@
       <c r="G79" t="n">
         <v>0</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5755,7 +5677,6 @@
       <c r="G80" t="n">
         <v>0</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5812,7 +5733,6 @@
       <c r="G81" t="n">
         <v>0</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5869,7 +5789,6 @@
       <c r="G82" t="n">
         <v>0</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5926,7 +5845,6 @@
       <c r="G83" t="n">
         <v>0</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5983,7 +5901,6 @@
       <c r="G84" t="n">
         <v>0</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6016,7 +5933,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6040,7 +5957,6 @@
       <c r="G85" t="n">
         <v>70</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6073,7 +5989,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6097,7 +6013,6 @@
       <c r="G86" t="n">
         <v>70</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6130,7 +6045,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6154,7 +6069,6 @@
       <c r="G87" t="n">
         <v>70</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6211,7 +6125,6 @@
       <c r="G88" t="n">
         <v>0</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6268,7 +6181,6 @@
       <c r="G89" t="n">
         <v>0</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6325,7 +6237,6 @@
       <c r="G90" t="n">
         <v>0</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6382,7 +6293,6 @@
       <c r="G91" t="n">
         <v>0</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6439,7 +6349,6 @@
       <c r="G92" t="n">
         <v>0</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6496,7 +6405,6 @@
       <c r="G93" t="n">
         <v>0</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6553,7 +6461,6 @@
       <c r="G94" t="n">
         <v>0</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6610,7 +6517,6 @@
       <c r="G95" t="n">
         <v>0</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6667,7 +6573,6 @@
       <c r="G96" t="n">
         <v>0</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6724,7 +6629,6 @@
       <c r="G97" t="n">
         <v>0</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6781,7 +6685,6 @@
       <c r="G98" t="n">
         <v>0</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6838,7 +6741,6 @@
       <c r="G99" t="n">
         <v>0</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6895,7 +6797,6 @@
       <c r="G100" t="n">
         <v>0</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6952,7 +6853,6 @@
       <c r="G101" t="n">
         <v>0</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7009,7 +6909,6 @@
       <c r="G102" t="n">
         <v>0</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7066,7 +6965,6 @@
       <c r="G103" t="n">
         <v>0</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7123,7 +7021,6 @@
       <c r="G104" t="n">
         <v>0</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7180,7 +7077,6 @@
       <c r="G105" t="n">
         <v>0</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7237,7 +7133,6 @@
       <c r="G106" t="n">
         <v>0</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7294,7 +7189,6 @@
       <c r="G107" t="n">
         <v>0</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7327,7 +7221,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7351,7 +7245,6 @@
       <c r="G108" t="n">
         <v>70</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7384,7 +7277,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7408,7 +7301,6 @@
       <c r="G109" t="n">
         <v>70</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7441,7 +7333,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7465,7 +7357,6 @@
       <c r="G110" t="n">
         <v>70</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7522,7 +7413,6 @@
       <c r="G111" t="n">
         <v>0</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7579,7 +7469,6 @@
       <c r="G112" t="n">
         <v>0</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7636,7 +7525,6 @@
       <c r="G113" t="n">
         <v>0</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7693,7 +7581,6 @@
       <c r="G114" t="n">
         <v>0</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7750,7 +7637,6 @@
       <c r="G115" t="n">
         <v>0</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7807,7 +7693,6 @@
       <c r="G116" t="n">
         <v>0</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7864,7 +7749,6 @@
       <c r="G117" t="n">
         <v>0</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7921,7 +7805,6 @@
       <c r="G118" t="n">
         <v>0</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7978,7 +7861,6 @@
       <c r="G119" t="n">
         <v>0</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8035,7 +7917,6 @@
       <c r="G120" t="n">
         <v>0</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8092,7 +7973,6 @@
       <c r="G121" t="n">
         <v>0</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8149,7 +8029,6 @@
       <c r="G122" t="n">
         <v>0</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8206,7 +8085,6 @@
       <c r="G123" t="n">
         <v>0</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8263,7 +8141,6 @@
       <c r="G124" t="n">
         <v>0</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8320,7 +8197,6 @@
       <c r="G125" t="n">
         <v>0</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8377,7 +8253,6 @@
       <c r="G126" t="n">
         <v>0</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8434,7 +8309,6 @@
       <c r="G127" t="n">
         <v>0</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8491,7 +8365,6 @@
       <c r="G128" t="n">
         <v>0</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8548,7 +8421,6 @@
       <c r="G129" t="n">
         <v>0</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8605,7 +8477,6 @@
       <c r="G130" t="n">
         <v>0</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8662,7 +8533,6 @@
       <c r="G131" t="n">
         <v>0</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8719,7 +8589,6 @@
       <c r="G132" t="n">
         <v>0</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8752,7 +8621,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8776,7 +8645,6 @@
       <c r="G133" t="n">
         <v>40.11</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8809,7 +8677,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8833,7 +8701,6 @@
       <c r="G134" t="n">
         <v>85.75</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8866,7 +8733,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8890,7 +8757,6 @@
       <c r="G135" t="n">
         <v>85.75</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8947,7 +8813,6 @@
       <c r="G136" t="n">
         <v>0</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9004,7 +8869,6 @@
       <c r="G137" t="n">
         <v>0</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9061,7 +8925,6 @@
       <c r="G138" t="n">
         <v>0</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9118,7 +8981,6 @@
       <c r="G139" t="n">
         <v>0</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9175,7 +9037,6 @@
       <c r="G140" t="n">
         <v>0</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9232,7 +9093,6 @@
       <c r="G141" t="n">
         <v>0</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9289,7 +9149,6 @@
       <c r="G142" t="n">
         <v>0</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9346,7 +9205,6 @@
       <c r="G143" t="n">
         <v>0</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9403,7 +9261,6 @@
       <c r="G144" t="n">
         <v>0</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9460,7 +9317,6 @@
       <c r="G145" t="n">
         <v>0</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9517,7 +9373,6 @@
       <c r="G146" t="n">
         <v>0</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9574,7 +9429,6 @@
       <c r="G147" t="n">
         <v>0</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9631,7 +9485,6 @@
       <c r="G148" t="n">
         <v>0</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9688,7 +9541,6 @@
       <c r="G149" t="n">
         <v>0</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9745,7 +9597,6 @@
       <c r="G150" t="n">
         <v>0</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9802,7 +9653,6 @@
       <c r="G151" t="n">
         <v>0</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9859,7 +9709,6 @@
       <c r="G152" t="n">
         <v>0</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9916,7 +9765,6 @@
       <c r="G153" t="n">
         <v>0</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9973,7 +9821,6 @@
       <c r="G154" t="n">
         <v>0</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10030,7 +9877,6 @@
       <c r="G155" t="n">
         <v>0</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10063,7 +9909,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10087,7 +9933,6 @@
       <c r="G156" t="n">
         <v>15</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10120,7 +9965,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10144,7 +9989,6 @@
       <c r="G157" t="n">
         <v>25.1</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10201,7 +10045,6 @@
       <c r="G158" t="n">
         <v>0</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10258,7 +10101,6 @@
       <c r="G159" t="n">
         <v>0</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10315,7 +10157,6 @@
       <c r="G160" t="n">
         <v>0</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10372,7 +10213,6 @@
       <c r="G161" t="n">
         <v>0</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10429,7 +10269,6 @@
       <c r="G162" t="n">
         <v>0</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10486,7 +10325,6 @@
       <c r="G163" t="n">
         <v>0</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10543,7 +10381,6 @@
       <c r="G164" t="n">
         <v>0</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10600,7 +10437,6 @@
       <c r="G165" t="n">
         <v>0</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10657,7 +10493,6 @@
       <c r="G166" t="n">
         <v>0</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10714,7 +10549,6 @@
       <c r="G167" t="n">
         <v>0</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10771,7 +10605,6 @@
       <c r="G168" t="n">
         <v>0</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10828,7 +10661,6 @@
       <c r="G169" t="n">
         <v>0</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10885,7 +10717,6 @@
       <c r="G170" t="n">
         <v>0</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10942,7 +10773,6 @@
       <c r="G171" t="n">
         <v>0</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10975,7 +10805,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10999,7 +10829,6 @@
       <c r="G172" t="n">
         <v>74.33</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11032,7 +10861,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Garden Apartment</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11056,7 +10885,6 @@
       <c r="G173" t="n">
         <v>29.08</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11113,7 +10941,6 @@
       <c r="G174" t="n">
         <v>0</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11170,7 +10997,6 @@
       <c r="G175" t="n">
         <v>0</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11227,7 +11053,6 @@
       <c r="G176" t="n">
         <v>0</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11284,7 +11109,6 @@
       <c r="G177" t="n">
         <v>0</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11341,7 +11165,6 @@
       <c r="G178" t="n">
         <v>0</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11398,7 +11221,6 @@
       <c r="G179" t="n">
         <v>0</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11455,7 +11277,6 @@
       <c r="G180" t="n">
         <v>0</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11512,7 +11333,6 @@
       <c r="G181" t="n">
         <v>0</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11569,7 +11389,6 @@
       <c r="G182" t="n">
         <v>0</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11626,7 +11445,6 @@
       <c r="G183" t="n">
         <v>0</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11683,7 +11501,6 @@
       <c r="G184" t="n">
         <v>0</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11740,7 +11557,6 @@
       <c r="G185" t="n">
         <v>0</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11797,7 +11613,6 @@
       <c r="G186" t="n">
         <v>0</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11854,7 +11669,6 @@
       <c r="G187" t="n">
         <v>0</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
